--- a/OOP/lab1/lab1.xlsx
+++ b/OOP/lab1/lab1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bitalir\Desktop\3 семестр\ООП\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bitalir\Desktop\3 семестр\OOP\lab1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2FD5179-7BBA-4987-8E23-A5A6ACF3B852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB3E2234-6DDA-44CA-8769-0754F223AF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{E1651109-4A8A-4C29-870F-F54CEFC87A8B}"/>
   </bookViews>
@@ -17,17 +17,26 @@
     <sheet name="Черный ящик" sheetId="2" r:id="rId2"/>
     <sheet name="БЯ" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="102">
   <si>
     <t>№ теста</t>
   </si>
@@ -398,12 +407,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -729,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F8947F4-3691-405A-AE1B-952A8E17B75C}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="45.6328125" customWidth="1"/>
@@ -741,260 +749,260 @@
     <col min="8" max="8" width="29.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5" t="s">
+      <c r="D2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+    </row>
+    <row r="3" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+    </row>
+    <row r="4" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5" t="s">
+      <c r="D4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5" t="s">
+      <c r="D5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+    </row>
+    <row r="6" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5" t="s">
+      <c r="D6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5" t="s">
+      <c r="D7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5" t="s">
+      <c r="D8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
+    </row>
+    <row r="9" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5" t="s">
+      <c r="D9" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
+    </row>
+    <row r="10" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5" t="s">
+      <c r="D10" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+    </row>
+    <row r="11" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5" t="s">
+      <c r="D11" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+    </row>
+    <row r="12" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5" t="s">
+      <c r="D12" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
+    </row>
+    <row r="13" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5" t="s">
+      <c r="D13" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+    </row>
+    <row r="14" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5" t="s">
+      <c r="D14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
+    </row>
+    <row r="15" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5" t="s">
+      <c r="D15" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1012,622 +1020,622 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="6" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
+      <c r="B2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
     </row>
     <row r="3" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
+      <c r="B3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
+      <c r="B12" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="O15" s="7"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7" t="s">
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
     </row>
     <row r="18" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
+      <c r="B18" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
     </row>
     <row r="19" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
+      <c r="B19" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
     </row>
     <row r="20" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
     </row>
     <row r="22" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
     </row>
     <row r="23" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
     </row>
     <row r="24" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
     </row>
     <row r="25" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="O25" s="7"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="O25" s="6"/>
     </row>
     <row r="26" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="7" t="s">
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="6" t="s">
         <v>3</v>
       </c>
     </row>
